--- a/mapping/PDTD_DTM/Mapping_FCT_RLOS_WORKSTEP_EVENT.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_RLOS_WORKSTEP_EVENT.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,15 +168,6 @@
     <font>
       <name val="Times New Roman"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -247,7 +238,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,9 +400,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -718,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +743,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact event log bước xử lý workflow RLOS tại PDTD_DTM, relay 1:1 từ STG_DTM.STG_FCT_RLOS_WORKSTEP_EVENT, bổ sung TAT/APPROVAL_FLAG/WORKSTEP_FLAG phái sinh</t>
+          <t>Bảng FACT nhật ký workflow mức nguyên tử của hệ RLOS tại PDTD_DTM, bê nguyên 1:1 từ STG_DTM.STG_FCT_RLOS_WORKSTEP_EVENT, bổ sung TAT_*/APPROVAL_FLAG/WORKSTEP_FLAG phái sinh</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -868,7 +856,7 @@
       </c>
       <c r="E16" s="6" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -881,12 +869,12 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>Ngày phiên bản ghi nhận</t>
+          <t>Ngày dữ liệu</t>
         </is>
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: STG_FCT_RLOS_WORKSTEP_EVENT. Ngày phiên bản được ghi nhận.</t>
+          <t>Ngày phiên bản được ghi nhận</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -913,7 +901,7 @@
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — khóa nghiệp vụ của dòng sự kiện, gộp WI_NAME+WORKSTEP_CODE+ENTRYDATE</t>
+          <t>Khóa nghiệp vụ của dòng sự kiện, gộp WI_NAME+WORKSTEP_CODE+ENTRYDATE</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -935,7 +923,7 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới bước xử lý - quyết định</t>
+          <t>Khóa bước &amp; quyết định</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
@@ -949,577 +937,577 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới người xử lý</t>
+          <t>Mã bước xử lý</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người xử lý của chính sự kiện này. KHÔNG nằm trong PK</t>
+          <t>Mã bước xử lý trên workflow</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>A.USER_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
+          <t>A.WORKSTEP_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>APPLICATION_SK</t>
+          <t>DECISION_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Mã quyết định bước</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
+          <t>CỘT MỚI — BK cạnh SK, nửa còn lại của BK composite DIM_RLOS_WORKSTEP_DECISION</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.APPLICATION_SK</t>
+          <t>A.DECISION_CODE</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>APPLICATION_SK</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng RLOS</t>
+          <t>Khóa tới DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
+          <t>A.APPLICATION_SK</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>WORKSTEP_CODE</t>
+          <t>WI_NAME</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Mã bước xử lý</t>
+          <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Mã bước xử lý trên workflow</t>
+          <t>Mã hồ sơ tín dụng RLOS</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>A.WORKSTEP_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>USER_SK</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Khóa người xử lý</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_LOS_USER, người xử lý của chính sự kiện này. KHÔNG nằm trong PK</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>A.USER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>ENTRYDATE</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Thời điểm vào bước</t>
         </is>
       </c>
-      <c r="D24" s="54" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Thời điểm hồ sơ vào bước xử lý</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.ENTRYDATE</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>EXITDATE</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Thời điểm ra bước</t>
         </is>
       </c>
-      <c r="D25" s="54" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Thời điểm hồ sơ ra khỏi bước xử lý. NULL nghĩa là hồ sơ đang nằm tại bước này</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.EXITDATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>USERNAME</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Tên tài khoản xử lý</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>Tên tài khoản người xử lý hồ sơ</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>A.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>REMARKS</t>
+          <t>USERNAME</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(4000)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Ghi chú bước xử lý</t>
+          <t>Tên tài khoản xử lý</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Ghi chú tại bước xử lý</t>
+          <t>Tên tài khoản người xử lý hồ sơ</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>A.REMARKS</t>
+          <t>A.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>REASON_CODE</t>
+          <t>REMARKS</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>VARCHAR2(4000)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Mã lý do hủy hồ sơ</t>
+          <t>Ghi chú bước xử lý</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Mã lý do hủy hồ sơ (chỉ RLOS có cột này)</t>
+          <t>Ghi chú tại bước xử lý</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.REASON_CODE</t>
+          <t>A.REMARKS</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>REASON_DESC</t>
+          <t>REASON_CODE</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Diễn giải lý do hủy hồ sơ</t>
+          <t>Mã lý do hủy hồ sơ</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Diễn giải lý do hủy hồ sơ (chỉ RLOS có cột này)</t>
+          <t>Mã lý do hủy hồ sơ (chỉ RLOS có cột này)</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.REASON_DESC</t>
+          <t>A.REASON_CODE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
+          <t>REASON_DESC</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Diễn giải lý do hủy</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Diễn giải lý do hủy hồ sơ (chỉ RLOS có cột này)</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>A.REASON_DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
           <t>TAT_SOURCE_SEC</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>NUMBER(12)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý hệ nguồn</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>TAT nguồn (giây)</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Thời gian xử lý do hệ nguồn ghi, đơn vị giây</t>
         </is>
       </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>A.TAT_SOURCE_SEC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>TAT_CALENDAR_HOUR</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(18,6)</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý lịch tự nhiên</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý theo lịch tự nhiên, đơn vị giờ — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH): Không trừ ngày nghỉ. Hồ sơ chưa có EXITDATE (còn treo tại bước) coi như xử lý đến hết ngày batch (23:59:59 của v_batch_date)</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>A.TAT_SOURCE_SEC / 3600, hoặc (CAST(NVL(A.EXITDATE, TRUNC(v_batch_date + 1) - INTERVAL '1' SECOND) AS DATE) - CAST(A.ENTRYDATE AS DATE)) * 24 nếu TAT_SOURCE_SEC rỗng</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
+          <t>TAT_CALENDAR_HOUR</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(18,6)</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>TAT theo giờ lịch</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo lịch tự nhiên, đơn vị giờ — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH). Không trừ ngày nghỉ. Hồ sơ chưa có EXITDATE (còn treo tại bước) coi như xử lý đến hết ngày batch (23:59:59 của v_batch_date).</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>A.TAT_SOURCE_SEC / 3600, hoặc (CAST(NVL(A.EXITDATE, TRUNC(v_batch_date + 1) - INTERVAL '1' SECOND) AS DATE) - CAST(A.ENTRYDATE AS DATE)) * 24 nếu TAT_SOURCE_SEC rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
           <t>TAT_WORKING_HOUR</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>NUMBER(18,6)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý giờ làm việc</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý theo giờ làm việc, đơn vị giờ — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH): Loại trừ ngày lễ, chiều thứ Bảy, cả ngày Chủ nhật; giờ tính 8-12 và 13-17. Hồ sơ chưa có EXITDATE (còn treo tại bước) coi như xử lý đến hết ngày batch (23:59:59 của v_batch_date)</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>TAT theo giờ làm việc</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo giờ làm việc, đơn vị giờ — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH). Loại trừ ngày lễ, chiều thứ Bảy, cả ngày Chủ nhật; giờ tính 8-12 và 13-17.</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>GET_BUSINESS_MINUTE(A.ENTRYDATE, NVL(A.EXITDATE, TRUNC(v_batch_date + 1) - INTERVAL '1' SECOND)) / 60</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>TAT_CPC_HOUR</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>NUMBER(18,6)</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý giờ SLA</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>Thời gian xử lý theo giờ cam kết SLA, đơn vị giờ — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH): Giờ theo cam kết SLA, tính 8-11:30 và 13:30-16:30. Hồ sơ chưa có EXITDATE (còn treo tại bước) coi như xử lý đến hết ngày batch (23:59:59 của v_batch_date)</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>TAT theo giờ SLA</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Thời gian xử lý theo giờ cam kết SLA, đơn vị giờ — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH). Giờ theo cam kết SLA, tính 8-11:30 và 13:30-16:30.</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>GET_BUSINESS_MINUTE_CPC(A.ENTRYDATE, NVL(A.EXITDATE, TRUNC(v_batch_date + 1) - INTERVAL '1' SECOND)) / 60</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>PROCESSED_DATE</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Ngày xử lý</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Ngày xử lý hồ sơ</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
         <is>
           <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên</t>
         </is>
       </c>
-      <c r="E34" s="31" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>A.PROCESSED_DATE</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>WF_PROCESSNAME</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Tên hệ thống workflow</t>
         </is>
       </c>
-      <c r="D35" s="54" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>Tên hệ thống workflow của instance đang đứng, đã lọc tài khoản test — cột thô</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
         <is>
           <t>A.WF_PROCESSNAME</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>WF_ACTIVITYNAME</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Bước hiện tại workflow</t>
         </is>
       </c>
-      <c r="D36" s="54" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>Bước hiện tại của instance workflow — cột thô</t>
         </is>
       </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>A.WF_ACTIVITYNAME</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>WF_CREATEDBY</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Người/hệ thống tạo bản ghi workflow</t>
-        </is>
-      </c>
-      <c r="D37" s="54" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Người tạo bản ghi workflow</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
         <is>
           <t>Mã người/hệ thống tạo bản ghi workflow — cột thô</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>A.WF_CREATEDBY</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="75" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>Cờ lần phê duyệt đầu/lại</t>
-        </is>
-      </c>
-      <c r="D38" s="54" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Cờ lần phê duyệt</t>
+        </is>
+      </c>
+      <c r="D39" s="54" t="inlineStr">
         <is>
           <t>Đánh dấu lần phê duyệt đầu hay lần phê duyệt lại — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH, cùng cơ chế đã áp dụng cho CLOS)</t>
         </is>
       </c>
-      <c r="E38" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN A.EXITDATE &lt;= (SELECT MIN(x.EXITDATE) FROM A x LEFT JOIN B wd ON wd.DIMENSION_KEY = x.WORKSTEP_DECISION_SK WHERE x.WI_NAME = A.WI_NAME AND x.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND wd.DECISION_CODE IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')) THEN 'First Approval' ELSE 'From Second Approval' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="240" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN A.EXITDATE &lt;= (SELECT MIN(x.EXITDATE) FROM STG_FCT_RLOS_WORKSTEP_EVENT x LEFT JOIN B wd ON wd.DIMENSION_KEY = x.WORKSTEP_DECISION_SK WHERE x.WI_NAME = A.WI_NAME AND x.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND wd.DECISION_CODE IN ('Send To HOSupport','Reject','Submit','Send To PostSanction','Submit To DisbursementMaker')) THEN 'First Approval' ELSE 'From Second Approval' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="255" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>WORKSTEP_FLAG</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>Trạng thái tổng hợp hồ sơ</t>
-        </is>
-      </c>
-      <c r="D39" s="54" t="inlineStr">
-        <is>
-          <t>Trạng thái tổng hợp hồ sơ dạng mô tả (trường FLAG của BC4, nhánh RLOS) — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH)</t>
-        </is>
-      </c>
-      <c r="E39" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN A.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND B.DECISION_CODE IN ('Send To HOSupport','Reject','Submit','Send To PostSanction') THEN 'Hồ sơ đã chuyển sang bước cấp PD và đã được phê duyệt' WHEN A.WF_CREATEDBY NOT IN ('10000380','10000020','10000420','10000140','10000100') AND A.WF_PROCESSNAME = 'RLOS' AND A.WF_ACTIVITYNAME IN ('CreditApproval','CreditCommittee') THEN 'Hồ sơ đã chuyển sang bước của cấp phê duyệt nhưng chưa PD' WHEN A.WORKSTEP_CODE = 'UnderwriterMaker' AND B.DECISION_CODE = 'Cancel' THEN 'Hồ sơ CVTĐ đã xử lý và chốt trạng thái tại bước của CVTĐ' WHEN (A.WF_CREATEDBY NOT IN ('10000380','10000020','10000420','10000140','10000100') AND A.WF_PROCESSNAME = 'RLOS' AND A.WF_ACTIVITYNAME = 'UnderwriterMaker') OR (A.WORKSTEP_CODE = 'UnderwriterMaker' AND B.DECISION_CODE = 'Send to UWChecker') THEN 'Hồ sơ CVTĐ đang/phải xử lý' WHEN A.WORKSTEP_CODE = 'UnderwriterMaker' AND B.DECISION_CODE IN ('Legal_Assessment','Additional_Doc_Required','Send_Back','Send_Back to DDE','Send Back DataInputerChecker','Send To Legal or FI or Phone Verification') THEN 'Hồ sơ CVTĐ đã xử lý nhưng chuyển/trả lại các bộ phận để bổ sung/làm rõ' ELSE NULL END</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERMAKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>User làm bước UnderwriterMaker</t>
+          <t>Trạng thái tổng hợp (FLAG)</t>
         </is>
       </c>
       <c r="D40" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterMaker'</t>
+          <t>Trạng thái tổng hợp hồ sơ dạng mô tả (trường FLAG của BC4, nhánh RLOS) — PHÁI SINH TẠI PDTD_DTM (chuyển từ SB_DWH). Khác CLOS ở nhánh 2 (PROCESSNAME='RLOS'), nhánh 4 (thêm OR DECISION_CODE='Send to UWChecker'), nhánh 5 (RLOS có 'Legal_Assessment'/'Send_Back', không có 'Send_Back to BranchSupport').</t>
         </is>
       </c>
       <c r="E40" s="31" t="inlineStr">
         <is>
-          <t>A.UNDERWRITERMAKER_USERMAKE</t>
+          <t>CASE WHEN A.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND WD.DECISION_CODE IN ('Send To HOSupport','Reject','Submit','Send To PostSanction') THEN 'Hồ sơ đã chuyển sang bước cấp PD và đã được phê duyệt' WHEN A.WF_CREATEDBY NOT IN ('10000380','10000020','10000420','10000140','10000100') AND A.WF_PROCESSNAME = 'RLOS' AND A.WF_ACTIVITYNAME IN ('CreditApproval','CreditCommittee') THEN 'Hồ sơ đã chuyển sang bước của cấp phê duyệt nhưng chưa PD' WHEN A.WORKSTEP_CODE = 'UnderwriterMaker' AND WD.DECISION_CODE = 'Cancel' THEN 'Hồ sơ CVTĐ đã xử lý và chốt trạng thái tại bước của CVTĐ' WHEN (A.WF_CREATEDBY NOT IN ('10000380','10000020','10000420','10000140','10000100') AND A.WF_PROCESSNAME = 'RLOS' AND A.WF_ACTIVITYNAME = 'UnderwriterMaker') OR (A.WORKSTEP_CODE = 'UnderwriterMaker' AND WD.DECISION_CODE = 'Send to UWChecker') THEN 'Hồ sơ CVTĐ đang/phải xử lý' WHEN A.WORKSTEP_CODE = 'UnderwriterMaker' AND WD.DECISION_CODE IN ('Legal_Assessment','Additional_Doc_Required','Send_Back','Send_Back to DDE','Send Back DataInputerChecker','Send To Legal or FI or Phone Verification') THEN 'Hồ sơ CVTĐ đã xử lý nhưng chuyển/trả lại các bộ phận để bổ sung/làm rõ' ELSE NULL END, LEFT JOIN B WD ON WD.DIMENSION_KEY = A.WORKSTEP_DECISION_SK</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="28" t="inlineStr">
         <is>
-          <t>UNDERWRITERCHECKER_USERMAKE</t>
+          <t>UNDERWRITERMAKER_USERMAKE</t>
         </is>
       </c>
       <c r="B41" s="25" t="inlineStr">
@@ -1529,66 +1517,71 @@
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>User làm bước UnderwriterChecker</t>
+          <t>User Maker CVTĐ</t>
         </is>
       </c>
       <c r="D41" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterChecker'</t>
+          <t>CỘT MỚI — chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterMaker'</t>
         </is>
       </c>
       <c r="E41" s="31" t="inlineStr">
         <is>
-          <t>A.UNDERWRITERCHECKER_USERMAKE</t>
+          <t>A.UNDERWRITERMAKER_USERMAKE</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="28" t="inlineStr">
         <is>
+          <t>UNDERWRITERCHECKER_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>User Checker CVTĐ</t>
+        </is>
+      </c>
+      <c r="D42" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='UnderwriterChecker'</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>A.UNDERWRITERCHECKER_USERMAKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
           <t>APPROVAL_USERMAKE</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B43" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước phê duyệt</t>
-        </is>
-      </c>
-      <c r="D42" s="54" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>User Maker phê duyệt</t>
+        </is>
+      </c>
+      <c r="D43" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — chỉ có giá trị khác NULL trên dòng event WORKSTEP_CODE='CreditCommittee' hoặc 'CreditApproval'</t>
         </is>
       </c>
-      <c r="E42" s="31" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>A.APPROVAL_USERMAKE</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="55" t="inlineStr">
-        <is>
-          <t>Điều kiện join giữa các bảng</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="51" t="n"/>
-      <c r="D45" s="54" t="n"/>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B ON B.DIMENSION_KEY = A.WORKSTEP_DECISION_SK</t>
         </is>
       </c>
     </row>
